--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.18445596456791</v>
+        <v>2.467474094242285</v>
       </c>
       <c r="D2" t="n">
-        <v>14.35285281738818</v>
+        <v>2.332338582825579</v>
       </c>
       <c r="E2" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F2" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.04299810021746</v>
+        <v>6.994487191285337</v>
       </c>
       <c r="D3" t="n">
-        <v>42.53395214708477</v>
+        <v>6.911767223901276</v>
       </c>
       <c r="E3" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F3" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.26173079106717</v>
+        <v>4.755031253548415</v>
       </c>
       <c r="D4" t="n">
-        <v>28.93527259246057</v>
+        <v>4.701981796274843</v>
       </c>
       <c r="E4" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F4" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.19221027675618</v>
+        <v>4.74373416997288</v>
       </c>
       <c r="D5" t="n">
-        <v>28.66159522985192</v>
+        <v>4.657509224850938</v>
       </c>
       <c r="E5" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F5" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.45223123053171</v>
+        <v>5.598487574961402</v>
       </c>
       <c r="D6" t="n">
-        <v>33.86617910269362</v>
+        <v>5.503254104187714</v>
       </c>
       <c r="E6" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F6" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.17634805626576</v>
+        <v>3.766156559143186</v>
       </c>
       <c r="D7" t="n">
-        <v>22.92095799944601</v>
+        <v>3.724655674909978</v>
       </c>
       <c r="E7" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F7" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.10360050089961</v>
+        <v>2.779335081396187</v>
       </c>
       <c r="D8" t="n">
-        <v>17.77926947917978</v>
+        <v>2.889131290366715</v>
       </c>
       <c r="E8" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F8" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.41627370792803</v>
+        <v>7.542644477538305</v>
       </c>
       <c r="D9" t="n">
-        <v>45.89699789336333</v>
+        <v>7.458262157671541</v>
       </c>
       <c r="E9" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F9" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.4616941517801</v>
+        <v>4.462525299664267</v>
       </c>
       <c r="D10" t="n">
-        <v>28.30585949502927</v>
+        <v>4.599702167942256</v>
       </c>
       <c r="E10" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F10" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.6341138597256</v>
+        <v>5.953043502205411</v>
       </c>
       <c r="D11" t="n">
-        <v>37.22130261784399</v>
+        <v>6.048461675399649</v>
       </c>
       <c r="E11" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F11" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.00004477359781</v>
+        <v>6.337507275709645</v>
       </c>
       <c r="D12" t="n">
-        <v>38.82893627132619</v>
+        <v>6.309702144090506</v>
       </c>
       <c r="E12" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F12" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.00003006592974</v>
+        <v>6.337504885713583</v>
       </c>
       <c r="D13" t="n">
-        <v>39.05537085441874</v>
+        <v>6.346497763843045</v>
       </c>
       <c r="E13" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F13" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.34605346379664</v>
+        <v>6.718733687866954</v>
       </c>
       <c r="D14" t="n">
-        <v>41.75027720144631</v>
+        <v>6.784420045235025</v>
       </c>
       <c r="E14" t="n">
-        <v>9.442038717787668</v>
+        <v>1.534331291640496</v>
       </c>
       <c r="F14" t="n">
-        <v>9.426971809902538</v>
+        <v>1.531882919109162</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
